--- a/outputs/execution-followthrough-20261024/site/dist/research.xlsx
+++ b/outputs/execution-followthrough-20261024/site/dist/research.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="市场调研" sheetId="1" r:id="R97247d3e21c94617"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对标产品" sheetId="2" r:id="Rd19133c8c17c4951"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机构名录" sheetId="3" r:id="R66097358c73e4004"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与缺口" sheetId="4" r:id="R347c5482d4134ce7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内容互动" sheetId="5" r:id="R5e1f2d7fcd8b4041"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="市场调研" sheetId="1" r:id="R05952c31dc68414b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对标产品" sheetId="2" r:id="Rfcde50fb2f5943e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机构名录" sheetId="3" r:id="Rc4bc30389cd743ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与缺口" sheetId="4" r:id="Rd28700ea17234386"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内容互动" sheetId="5" r:id="R3d3b644192b54c0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StudyTable0" displayName="StudyTable0" ref="A5:G26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StudyTable0" displayName="StudyTable0" ref="A5:G32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="分类"/>
     <x:tableColumn id="2" name="指标"/>
@@ -169,7 +169,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="StudyTable1" displayName="StudyTable1" ref="A5:I55" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="StudyTable1" displayName="StudyTable1" ref="A5:I57" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="方向"/>
     <x:tableColumn id="2" name="机构及产品"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="StudyTable2" displayName="StudyTable2" ref="A5:F70" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="StudyTable2" displayName="StudyTable2" ref="A5:F71" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="机构"/>
     <x:tableColumn id="2" name="主要组织方式"/>
@@ -200,7 +200,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="StudyTable3" displayName="StudyTable3" ref="A5:F155" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="StudyTable3" displayName="StudyTable3" ref="A5:F166" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="资料"/>
@@ -977,6 +977,136 @@
         <x:v>查看原文 E01</x:v>
       </x:c>
     </x:row>
+    <x:row r="27" ht="62.5" customHeight="1">
+      <x:c r="A27" s="10" t="str">
+        <x:v>研究结论</x:v>
+      </x:c>
+      <x:c r="B27" s="10" t="str">
+        <x:v>定位</x:v>
+      </x:c>
+      <x:c r="C27" s="13"/>
+      <x:c r="D27" s="10" t="str">
+        <x:v>研究判断</x:v>
+      </x:c>
+      <x:c r="E27" s="10" t="str">
+        <x:v>本版综合分析</x:v>
+      </x:c>
+      <x:c r="F27" s="10" t="str">
+        <x:v>建议以持续线下社群为主体，商业、婚恋与旅行按参加目的分产品。 先统一客户服务和活动日历；单身互选、商务交流和普通同行各自说明报名目的。</x:v>
+      </x:c>
+      <x:c r="G27" s="10" t="str">
+        <x:v>微信小程序实查
+见来源与缺口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="62.5" customHeight="1">
+      <x:c r="A28" s="11" t="str">
+        <x:v>研究结论</x:v>
+      </x:c>
+      <x:c r="B28" s="11" t="str">
+        <x:v>第一批付费者</x:v>
+      </x:c>
+      <x:c r="C28" s="12"/>
+      <x:c r="D28" s="11" t="str">
+        <x:v>研究判断</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="str">
+        <x:v>本版综合分析</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="str">
+        <x:v>优先找已有明确见人或同行需求、且时间与预算匹配的人。A8用于资格核验，购买动机另问。 分别招募经营交流者与有恋爱意愿的单身者；实际年龄和城市以可触达客户确认。</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="str">
+        <x:v>微信小程序实查
+见来源与缺口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="62.5" customHeight="1">
+      <x:c r="A29" s="10" t="str">
+        <x:v>研究结论</x:v>
+      </x:c>
+      <x:c r="B29" s="10" t="str">
+        <x:v>再次参加</x:v>
+      </x:c>
+      <x:c r="C29" s="13"/>
+      <x:c r="D29" s="10" t="str">
+        <x:v>研究判断</x:v>
+      </x:c>
+      <x:c r="E29" s="10" t="str">
+        <x:v>本版综合分析</x:v>
+      </x:c>
+      <x:c r="F29" s="10" t="str">
+        <x:v>可复用的是持续匹配与共同主题，宜让客人记得上次认识了谁、下次为什么见。 保留同意后可延续的联系与活动偏好；下一次邀请说明具体话题或同行者理由。</x:v>
+      </x:c>
+      <x:c r="G29" s="10" t="str">
+        <x:v>微信小程序实查
+见来源与缺口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="62.5" customHeight="1">
+      <x:c r="A30" s="11" t="str">
+        <x:v>研究结论</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="str">
+        <x:v>旅行产品</x:v>
+      </x:c>
+      <x:c r="C30" s="12"/>
+      <x:c r="D30" s="11" t="str">
+        <x:v>研究判断</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="str">
+        <x:v>本版综合分析</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="str">
+        <x:v>应把同行组织、现场主持与目的地交付分别写进产品。 旅行报价逐项列筛选、主持和地面服务；由谁负责招募、住宿交通和异常处理要明确。</x:v>
+      </x:c>
+      <x:c r="G30" s="15" t="str">
+        <x:v>查看原文 R04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="62.5" customHeight="1">
+      <x:c r="A31" s="10" t="str">
+        <x:v>研究结论</x:v>
+      </x:c>
+      <x:c r="B31" s="10" t="str">
+        <x:v>收费顺序</x:v>
+      </x:c>
+      <x:c r="C31" s="13"/>
+      <x:c r="D31" s="10" t="str">
+        <x:v>研究判断</x:v>
+      </x:c>
+      <x:c r="E31" s="10" t="str">
+        <x:v>本版综合分析</x:v>
+      </x:c>
+      <x:c r="F31" s="10" t="str">
+        <x:v>建议先按场、按团测试，再决定哪类服务适合会籍。 当前1680／680／19800元只作测算。先问客户最近付过什么钱，再验证具体规格愿付。</x:v>
+      </x:c>
+      <x:c r="G31" s="10" t="str">
+        <x:v>微信小程序实查
+见来源与缺口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="62.5" customHeight="1">
+      <x:c r="A32" s="11" t="str">
+        <x:v>研究结论</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="str">
+        <x:v>对标用途</x:v>
+      </x:c>
+      <x:c r="C32" s="12"/>
+      <x:c r="D32" s="11" t="str">
+        <x:v>研究判断</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="str">
+        <x:v>本版综合分析</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="str">
+        <x:v>启动组织优先学BoL与Founder Feast；高价顾问与旅行分别学能力。 钻石作成熟筛选顾问参照；奇语作小团内容参照；OWR作行前、支付与退改参照。</x:v>
+      </x:c>
+      <x:c r="G32" s="15" t="str">
+        <x:v>查看原文 C01</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A2:G2"/>
@@ -1004,10 +1134,12 @@
     <x:hyperlink xmlns:ns19="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" ns19:id="rIdStudy19"/>
     <x:hyperlink xmlns:ns20="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" ns20:id="rIdStudy20"/>
     <x:hyperlink xmlns:ns21="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" ns21:id="rIdStudy21"/>
+    <x:hyperlink xmlns:ns22="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" ns22:id="rIdStudy22"/>
+    <x:hyperlink xmlns:ns23="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" ns23:id="rIdStudy23"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccc6ade9a35c4434"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcce1dc3a5ea6440b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1193,7 +1325,7 @@
         <x:v>匿名嘉宾及活动内容→微信详情申请。展示已售29、剩5；实到、收入成本和复购未披露。</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>婚恋启动主对标：学习具体审核与半天交付。</x:v>
+        <x:v>单身私宴启动对标；1688为该场展示价，会员价未公开；学准入、主持和互选。</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
         <x:v>微信小程序实查
@@ -1411,7 +1543,7 @@
         <x:v>查看原文 QI</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="62.5" customHeight="1">
+    <x:row r="16" ht="93.5" customHeight="1">
       <x:c r="A16" s="11" t="str">
         <x:v>社交旅行</x:v>
       </x:c>
@@ -1424,7 +1556,7 @@
       </x:c>
       <x:c r="D16" s="11" t="str">
         <x:v>1400英镑／人
-四星双床、早餐及2午2晚、接送机、活动、主持及当地专家；国际机票另购。</x:v>
+四星双床、早餐及2午2晚、接送机、活动、主持及当地专家；国际机票另购。 独住另225英镑后为1625英镑／人，未含国际机票、保险及未列餐饮。</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
         <x:v>30—49岁，官网称90%独自报名；不是单身核验。欢迎内外向、愿参与文化和美食体验者；未设职业收入资产线。</x:v>
@@ -1483,8 +1615,7 @@
       </x:c>
       <x:c r="C18" s="12"/>
       <x:c r="D18" s="11" t="str">
-        <x:v>定金200英镑
-出发70天前付尾款；具体退改按该团条款。2026年末和2027年团期在列。</x:v>
+        <x:v>英镑定金200或美元250；尾款出发前70天付清，不足70天报名全款。取消超过70天定金可转后续行程；69—30天扣50%，不足30天扣100%。</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
         <x:v>30—49岁，官网称90%独自报名；不是单身核验。欢迎内外向、愿参与文化和美食体验者；未设职业收入资产线。</x:v>
@@ -1499,10 +1630,10 @@
         <x:v>国外交付主对标：学行前服务、房型与付款节点。</x:v>
       </x:c>
       <x:c r="I18" s="15" t="str">
-        <x:v>查看原文 OWR</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="47" customHeight="1">
+        <x:v>查看原文 R05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="78" customHeight="1">
       <x:c r="A19" s="10" t="str">
         <x:v>商业社交</x:v>
       </x:c>
@@ -1518,22 +1649,22 @@
 仅会员与匹配，餐酒另付</x:v>
       </x:c>
       <x:c r="E19" s="10" t="str">
-        <x:v>创业者；具体年龄收入资产未设公开线</x:v>
+        <x:v>核心为创业者、CEO、联合创始人及经营者；流程页亦欢迎投资人、医生、教授、运动员、艺术家等。申请考察正在做什么和想认识谁。没有年龄、婚姻、资产或收入统一数值门槛。</x:v>
       </x:c>
       <x:c r="F19" s="10" t="str">
-        <x:v>审核后付费→隔周周四5人桌→前一天揭晓餐厅及桌友</x:v>
+        <x:v>申请人工审核→App选隔周周四晚餐→按行业、阶段和问题配桌→前24小时公布同桌餐厅→用餐自付餐酒→App延续联系。提前24小时可免费取消晚餐预约；FAQ列未通知缺席50加元。</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
         <x:v>3城在列；无付费会员及利润</x:v>
       </x:c>
       <x:c r="H19" s="10" t="str">
-        <x:v>主对标；价格与App交叉核对</x:v>
+        <x:v>启动形式重点：学小桌筛选与匹配、餐费分账及后续联系，不把其职业范围等同A8客群。</x:v>
       </x:c>
       <x:c r="I19" s="17" t="str">
-        <x:v>查看原文 B12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="47" customHeight="1">
+        <x:v>查看原文 R03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="78" customHeight="1">
       <x:c r="A20" s="11" t="str">
         <x:v>商业社交</x:v>
       </x:c>
@@ -1549,22 +1680,22 @@
 同一会籍，App购买</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>同上</x:v>
+        <x:v>核心为创业者、CEO、联合创始人及经营者；流程页亦欢迎投资人、医生、教授、运动员、艺术家等。申请考察正在做什么和想认识谁。没有年龄、婚姻、资产或收入统一数值门槛。</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
-        <x:v>同上</x:v>
+        <x:v>申请人工审核→App选隔周周四晚餐→按行业、阶段和问题配桌→前24小时公布同桌餐厅→用餐自付餐酒→App延续联系。提前24小时可免费取消晚餐预约；FAQ列未通知缺席50加元。</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
         <x:v>同上</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str">
-        <x:v>主对标；同一会籍不同付款周期</x:v>
+        <x:v>启动形式重点：学小桌筛选与匹配、餐费分账及后续联系，不把其职业范围等同A8客群。</x:v>
       </x:c>
       <x:c r="I20" s="15" t="str">
-        <x:v>查看原文 B12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="47" customHeight="1">
+        <x:v>查看原文 R03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="78" customHeight="1">
       <x:c r="A21" s="10" t="str">
         <x:v>商业社交</x:v>
       </x:c>
@@ -1580,19 +1711,19 @@
 同一会籍，App购买</x:v>
       </x:c>
       <x:c r="E21" s="10" t="str">
-        <x:v>同上</x:v>
+        <x:v>核心为创业者、CEO、联合创始人及经营者；流程页亦欢迎投资人、医生、教授、运动员、艺术家等。申请考察正在做什么和想认识谁。没有年龄、婚姻、资产或收入统一数值门槛。</x:v>
       </x:c>
       <x:c r="F21" s="10" t="str">
-        <x:v>同上</x:v>
+        <x:v>申请人工审核→App选隔周周四晚餐→按行业、阶段和问题配桌→前24小时公布同桌餐厅→用餐自付餐酒→App延续联系。提前24小时可免费取消晚餐预约；FAQ列未通知缺席50加元。</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
         <x:v>同上</x:v>
       </x:c>
       <x:c r="H21" s="10" t="str">
-        <x:v>主对标</x:v>
+        <x:v>启动形式重点：学小桌筛选与匹配、餐费分账及后续联系，不把其职业范围等同A8客群。</x:v>
       </x:c>
       <x:c r="I21" s="17" t="str">
-        <x:v>查看原文 B12</x:v>
+        <x:v>查看原文 R03</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="47" customHeight="1">
@@ -2329,7 +2460,7 @@
         <x:v>查看原文 FLASH</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="62.5" customHeight="1">
+    <x:row r="46" ht="78" customHeight="1">
       <x:c r="A46" s="11" t="str">
         <x:v>社交旅行</x:v>
       </x:c>
@@ -2341,26 +2472,25 @@
         <x:v>895</x:v>
       </x:c>
       <x:c r="D46" s="11" t="str">
-        <x:v>欧元起／人；最高1125
-2027团期按房型；厨师全餐和住宿；接驳10—30另付；标题5日与5晚含项待确认</x:v>
+        <x:v>欧元／人；2027年5月20—25日五晚。自带帐篷895；双人帐篷或指定双住995；房屋独住1095；小屋独住1125，伴侣双住每人995。另先付定金300。含全餐与场地活动，外出交通等另计。</x:v>
       </x:c>
       <x:c r="E46" s="11" t="str">
-        <x:v>过往23—68岁；可与伴侣或朋友；无资产收入线</x:v>
+        <x:v>16—20人活动设计；男女、不同关系状态与文化背景均可。官网往期23—68岁；有33岁设计师、27岁创业者、47岁教师的公开样例；无资产收入门槛。</x:v>
       </x:c>
       <x:c r="F46" s="11" t="str">
-        <x:v>城市活动→度假报名→收存手机→散步创作及共同晚餐；16—20人</x:v>
+        <x:v>选择房型并申请审核→付300欧元定金→按通知付尾款→到场收存手机→自主散步、创作与共同用餐→离场。活动可选择参加，主办方社群主持人与农场共同交付。</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
-        <x:v>官网500+活动、2万+Offliners为无截止期自述</x:v>
+        <x:v>城市社区日历导向度假售票；2024年起合作为主办方自述，未取得本团实际人数和利润。网页列房型余位不作为到场数。</x:v>
       </x:c>
       <x:c r="H46" s="11" t="str">
-        <x:v>保留城市社群延伸度假的重点形式；非婚恋和A8审核</x:v>
+        <x:v>社群延伸旅行的重要形式参照。分担客户组织和场地餐饮交付；并非婚恋或A8筛选产品。</x:v>
       </x:c>
       <x:c r="I46" s="15" t="str">
-        <x:v>查看原文 OFF</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="62.5" customHeight="1">
+        <x:v>查看原文 R12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="78" customHeight="1">
       <x:c r="A47" s="10" t="str">
         <x:v>社交旅行</x:v>
       </x:c>
@@ -2376,13 +2506,13 @@
 8晚、8早3午4晚、行程和领队；独住2026加1999起，2027加2199起；机票接送保险另付</x:v>
       </x:c>
       <x:c r="E47" s="10" t="str">
-        <x:v>25—39岁专业人士为前轮品牌定位，无A8门槛</x:v>
+        <x:v>25—39岁，品牌自述平均30岁、多为27—34岁；80%独自报名、70%—80%女性、60%自述单身且愿交友、75%大城市。未列调查年份及收入资产统计。</x:v>
       </x:c>
       <x:c r="F47" s="10" t="str">
-        <x:v>选择日期房型→预订→领队和文化体验；逐团确认</x:v>
+        <x:v>选择日期房型→预订→领队和文化体验；逐团确认 客户填旅行档案；常规分期于出发前95／65／35天累计支付50%／75%／100%。日本适用95天取消政策，其他目的地按具体条款。</x:v>
       </x:c>
       <x:c r="G47" s="10" t="str">
-        <x:v>当前有具体线路报价；实到和利润未公开</x:v>
+        <x:v>官网现行客群及费用规则可核；回头客后续旅行减200美元，不能据此推算复购率。</x:v>
       </x:c>
       <x:c r="H47" s="10" t="str">
         <x:v>保留精品地面报价及同龄同行参照</x:v>
@@ -2617,6 +2747,66 @@
       </x:c>
       <x:c r="I55" s="17" t="str">
         <x:v>查看原文 X08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="78" customHeight="1">
+      <x:c r="A56" s="11" t="str">
+        <x:v>旅行供给参照</x:v>
+      </x:c>
+      <x:c r="B56" s="11" t="str">
+        <x:v>32号
+海南环岛六日私家团</x:v>
+      </x:c>
+      <x:c r="C56" s="12" t="n">
+        <x:v>5980</x:v>
+      </x:c>
+      <x:c r="D56" s="11" t="str">
+        <x:v>人民币起／人；5晚基础房两人同住、5早1晚餐、行程车及门票体验；海口往返大交通、单房差与其他正餐另付。2人起订，不与陌生人拼团。</x:v>
+      </x:c>
+      <x:c r="E56" s="11" t="str">
+        <x:v>家庭、情侣及自有同行者；职业收入资产未设统一门槛；其中踏瀑体验55岁以上不可参加，属项目限制。</x:v>
+      </x:c>
+      <x:c r="F56" s="11" t="str">
+        <x:v>海口接机→东线咖啡与椰园→三亚海上体验及雨林→棋子湾→海口送站。按人数5／7／9座，导游兼司机。</x:v>
+      </x:c>
+      <x:c r="G56" s="11" t="str">
+        <x:v>官网自述100万累计用户、85%来自推荐、600余在册领队；无对应统计期或独立审计。</x:v>
+      </x:c>
+      <x:c r="H56" s="11" t="str">
+        <x:v>用于核对地面含项、房型、车与退改。2人独立成行产品不承担替客户寻找新同行者的工作。</x:v>
+      </x:c>
+      <x:c r="I56" s="15" t="str">
+        <x:v>查看原文 R09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="62.5" customHeight="1">
+      <x:c r="A57" s="10" t="str">
+        <x:v>旅行供给参照</x:v>
+      </x:c>
+      <x:c r="B57" s="10" t="str">
+        <x:v>东方中华行
+三亚四天私人包车</x:v>
+      </x:c>
+      <x:c r="C57" s="13" t="n">
+        <x:v>2748</x:v>
+      </x:c>
+      <x:c r="D57" s="10" t="str">
+        <x:v>人民币起／人；含行程住宿、当地专车接送和所列首道门票；未指定11月19日或瑞吉房型，不能当同条件团体报价。</x:v>
+      </x:c>
+      <x:c r="E57" s="10" t="str">
+        <x:v>页面定位2—30人的家庭及团队；不设公开单身、资产或职业筛选。</x:v>
+      </x:c>
+      <x:c r="F57" s="10" t="str">
+        <x:v>到达接机；第二天九选二景点；第三天七选一体验；第四天送站。填需求后顾问沟通再确认方案及付款。</x:v>
+      </x:c>
+      <x:c r="G57" s="10" t="str">
+        <x:v>当前有产品和询价入口，未取得该产品实际客户量、收入和利润。</x:v>
+      </x:c>
+      <x:c r="H57" s="10" t="str">
+        <x:v>仅作旅游供应与产品规格参照，不新增为高端社群主对标。</x:v>
+      </x:c>
+      <x:c r="I57" s="17" t="str">
+        <x:v>查看原文 R10</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2672,10 +2862,12 @@
     <x:hyperlink xmlns:ns45="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" ns45:id="rIdStudy45"/>
     <x:hyperlink xmlns:ns46="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" ns46:id="rIdStudy46"/>
     <x:hyperlink xmlns:ns47="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" ns47:id="rIdStudy47"/>
+    <x:hyperlink xmlns:ns48="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" ns48:id="rIdStudy48"/>
+    <x:hyperlink xmlns:ns49="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" ns49:id="rIdStudy49"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd74d846d58d0437f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recfb60cf74954f82"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2712,7 +2904,7 @@
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>65条机构与品牌线索覆盖原有研究和新增候选；主对标、成熟参照与未深挖候选在用途栏区分。正和岛和优家荟按要求退出。</x:v>
+        <x:v>66条机构与品牌线索覆盖原有研究和新增候选；主对标、成熟参照与未深挖候选在用途栏区分。正和岛和优家荟按要求退出。</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -4045,6 +4237,26 @@
         <x:v>新增婚恋旅行候选；不能从高净值标签直接升为主对标</x:v>
       </x:c>
       <x:c r="F70" s="11" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="93.5" customHeight="1">
+      <x:c r="A71" s="10" t="str">
+        <x:v>东方中华行</x:v>
+      </x:c>
+      <x:c r="B71" s="10" t="str">
+        <x:v>私人包车及定制旅行</x:v>
+      </x:c>
+      <x:c r="C71" s="10" t="str">
+        <x:v>中国多目的地</x:v>
+      </x:c>
+      <x:c r="D71" s="10" t="str">
+        <x:v>家庭与自有团队</x:v>
+      </x:c>
+      <x:c r="E71" s="10" t="str">
+        <x:v>供应及含项参照；非高端社群主对标</x:v>
+      </x:c>
+      <x:c r="F71" s="10" t="str">
         <x:v>查看原文</x:v>
       </x:c>
     </x:row>
@@ -4118,10 +4330,11 @@
     <x:hyperlink xmlns:ns62="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" ns62:id="rIdStudy62"/>
     <x:hyperlink xmlns:ns63="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" ns63:id="rIdStudy63"/>
     <x:hyperlink xmlns:ns64="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" ns64:id="rIdStudy64"/>
+    <x:hyperlink xmlns:ns65="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" ns65:id="rIdStudy65"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe9ca1db3dee438f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89f85f6b5bb24504"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7168,115 +7381,335 @@
         <x:v>微信小程序或私有资料，无网页链接</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="32" customHeight="1">
-      <x:c r="A159" s="19" t="str">
+    <x:row r="156" ht="47" customHeight="1">
+      <x:c r="A156" s="11" t="str">
+        <x:v>R01</x:v>
+      </x:c>
+      <x:c r="B156" s="11" t="str">
+        <x:v>Founder Feast匹配与交付</x:v>
+      </x:c>
+      <x:c r="C156" s="11" t="str">
+        <x:v>本轮Crawl4AI官网或主办方售票页原文</x:v>
+      </x:c>
+      <x:c r="D156" s="11" t="d">
+        <x:v>2026-10-24T07:57:47.869Z</x:v>
+      </x:c>
+      <x:c r="E156" s="11" t="str">
+        <x:v>8805字；原文及SHA-256留档。客户比例与规模为品牌自述，未列调查年份的保留原口径。</x:v>
+      </x:c>
+      <x:c r="F156" s="11" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="47" customHeight="1">
+      <x:c r="A157" s="10" t="str">
+        <x:v>R03</x:v>
+      </x:c>
+      <x:c r="B157" s="10" t="str">
+        <x:v>Founder Feast常见问题</x:v>
+      </x:c>
+      <x:c r="C157" s="10" t="str">
+        <x:v>本轮Crawl4AI官网或主办方售票页原文</x:v>
+      </x:c>
+      <x:c r="D157" s="10" t="d">
+        <x:v>2026-10-24T07:58:12.850Z</x:v>
+      </x:c>
+      <x:c r="E157" s="10" t="str">
+        <x:v>10411字；原文及SHA-256留档。客户比例与规模为品牌自述，未列调查年份的保留原口径。</x:v>
+      </x:c>
+      <x:c r="F157" s="10" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="47" customHeight="1">
+      <x:c r="A158" s="11" t="str">
+        <x:v>R04</x:v>
+      </x:c>
+      <x:c r="B158" s="11" t="str">
+        <x:v>OWR旅行适配条件</x:v>
+      </x:c>
+      <x:c r="C158" s="11" t="str">
+        <x:v>本轮Crawl4AI官网或主办方售票页原文</x:v>
+      </x:c>
+      <x:c r="D158" s="11" t="d">
+        <x:v>2026-10-24T07:58:24.580Z</x:v>
+      </x:c>
+      <x:c r="E158" s="11" t="str">
+        <x:v>11044字；原文及SHA-256留档。客户比例与规模为品牌自述，未列调查年份的保留原口径。</x:v>
+      </x:c>
+      <x:c r="F158" s="11" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="47" customHeight="1">
+      <x:c r="A159" s="10" t="str">
+        <x:v>R05</x:v>
+      </x:c>
+      <x:c r="B159" s="10" t="str">
+        <x:v>OWR预订付款取消条款</x:v>
+      </x:c>
+      <x:c r="C159" s="10" t="str">
+        <x:v>本轮Crawl4AI官网或主办方售票页原文</x:v>
+      </x:c>
+      <x:c r="D159" s="10" t="d">
+        <x:v>2026-10-24T07:58:40.515Z</x:v>
+      </x:c>
+      <x:c r="E159" s="10" t="str">
+        <x:v>23432字；原文及SHA-256留档。客户比例与规模为品牌自述，未列调查年份的保留原口径。</x:v>
+      </x:c>
+      <x:c r="F159" s="10" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="47" customHeight="1">
+      <x:c r="A160" s="11" t="str">
+        <x:v>R06</x:v>
+      </x:c>
+      <x:c r="B160" s="11" t="str">
+        <x:v>FTLO客群及复购优惠</x:v>
+      </x:c>
+      <x:c r="C160" s="11" t="str">
+        <x:v>本轮Crawl4AI官网或主办方售票页原文</x:v>
+      </x:c>
+      <x:c r="D160" s="11" t="d">
+        <x:v>2026-10-24T07:58:52.836Z</x:v>
+      </x:c>
+      <x:c r="E160" s="11" t="str">
+        <x:v>87519字；原文及SHA-256留档。客户比例与规模为品牌自述，未列调查年份的保留原口径。</x:v>
+      </x:c>
+      <x:c r="F160" s="11" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="47" customHeight="1">
+      <x:c r="A161" s="10" t="str">
+        <x:v>R07</x:v>
+      </x:c>
+      <x:c r="B161" s="10" t="str">
+        <x:v>The Offline Club法国社群度假</x:v>
+      </x:c>
+      <x:c r="C161" s="10" t="str">
+        <x:v>本轮Crawl4AI官网或主办方售票页原文</x:v>
+      </x:c>
+      <x:c r="D161" s="10" t="d">
+        <x:v>2026-10-24T07:59:07.950Z</x:v>
+      </x:c>
+      <x:c r="E161" s="10" t="str">
+        <x:v>29038字；原文及SHA-256留档。客户比例与规模为品牌自述，未列调查年份的保留原口径。</x:v>
+      </x:c>
+      <x:c r="F161" s="10" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="47" customHeight="1">
+      <x:c r="A162" s="11" t="str">
+        <x:v>R08</x:v>
+      </x:c>
+      <x:c r="B162" s="11" t="str">
+        <x:v>32号组织与经营自述</x:v>
+      </x:c>
+      <x:c r="C162" s="11" t="str">
+        <x:v>本轮Crawl4AI官网或主办方售票页原文</x:v>
+      </x:c>
+      <x:c r="D162" s="11" t="d">
+        <x:v>2026-10-24T07:59:23.115Z</x:v>
+      </x:c>
+      <x:c r="E162" s="11" t="str">
+        <x:v>9275字；原文及SHA-256留档。客户比例与规模为品牌自述，未列调查年份的保留原口径。</x:v>
+      </x:c>
+      <x:c r="F162" s="11" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="47" customHeight="1">
+      <x:c r="A163" s="10" t="str">
+        <x:v>R09</x:v>
+      </x:c>
+      <x:c r="B163" s="10" t="str">
+        <x:v>32号海南六日私家团</x:v>
+      </x:c>
+      <x:c r="C163" s="10" t="str">
+        <x:v>本轮Crawl4AI官网或主办方售票页原文</x:v>
+      </x:c>
+      <x:c r="D163" s="10" t="d">
+        <x:v>2026-10-24T07:59:38.411Z</x:v>
+      </x:c>
+      <x:c r="E163" s="10" t="str">
+        <x:v>23034字；原文及SHA-256留档。客户比例与规模为品牌自述，未列调查年份的保留原口径。</x:v>
+      </x:c>
+      <x:c r="F163" s="10" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="47" customHeight="1">
+      <x:c r="A164" s="11" t="str">
+        <x:v>R10</x:v>
+      </x:c>
+      <x:c r="B164" s="11" t="str">
+        <x:v>三亚四天私家包车产品</x:v>
+      </x:c>
+      <x:c r="C164" s="11" t="str">
+        <x:v>本轮Crawl4AI官网或主办方售票页原文</x:v>
+      </x:c>
+      <x:c r="D164" s="11" t="d">
+        <x:v>2026-10-24T07:59:51.015Z</x:v>
+      </x:c>
+      <x:c r="E164" s="11" t="str">
+        <x:v>19014字；原文及SHA-256留档。客户比例与规模为品牌自述，未列调查年份的保留原口径。</x:v>
+      </x:c>
+      <x:c r="F164" s="11" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="47" customHeight="1">
+      <x:c r="A165" s="10" t="str">
+        <x:v>R11</x:v>
+      </x:c>
+      <x:c r="B165" s="10" t="str">
+        <x:v>Founder Feast现行价格复核</x:v>
+      </x:c>
+      <x:c r="C165" s="10" t="str">
+        <x:v>本轮Crawl4AI官网或主办方售票页原文</x:v>
+      </x:c>
+      <x:c r="D165" s="10" t="d">
+        <x:v>2026-10-24T08:00:08.143Z</x:v>
+      </x:c>
+      <x:c r="E165" s="10" t="str">
+        <x:v>7642字；原文及SHA-256留档。客户比例与规模为品牌自述，未列调查年份的保留原口径。</x:v>
+      </x:c>
+      <x:c r="F165" s="10" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="47" customHeight="1">
+      <x:c r="A166" s="11" t="str">
+        <x:v>R12</x:v>
+      </x:c>
+      <x:c r="B166" s="11" t="str">
+        <x:v>The Offline Club五月法国房型与付款退改</x:v>
+      </x:c>
+      <x:c r="C166" s="11" t="str">
+        <x:v>本轮Crawl4AI官网或主办方售票页原文</x:v>
+      </x:c>
+      <x:c r="D166" s="11" t="d">
+        <x:v>2026-10-24T08:00:42.473Z</x:v>
+      </x:c>
+      <x:c r="E166" s="11" t="str">
+        <x:v>8961字；原文及SHA-256留档。客户比例与规模为品牌自述，未列调查年份的保留原口径。</x:v>
+      </x:c>
+      <x:c r="F166" s="11" t="str">
+        <x:v>查看原文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="32" customHeight="1">
+      <x:c r="A170" s="19" t="str">
         <x:v>对象</x:v>
       </x:c>
-      <x:c r="B159" s="19" t="str">
+      <x:c r="B170" s="19" t="str">
         <x:v>缺少什么</x:v>
       </x:c>
-      <x:c r="C159" s="19" t="str">
+      <x:c r="C170" s="19" t="str">
         <x:v>怎样补齐</x:v>
       </x:c>
-      <x:c r="D159" s="19" t="str">
+      <x:c r="D170" s="19" t="str">
         <x:v>当前处理</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="95" customHeight="1">
-      <x:c r="A160" s="20" t="str">
+    <x:row r="171" ht="95" customHeight="1">
+      <x:c r="A171" s="20" t="str">
         <x:v>BoL商务会籍</x:v>
       </x:c>
-      <x:c r="B160" s="20" t="str">
+      <x:c r="B171" s="20" t="str">
         <x:v>付费会员、续费、实际履约及运动含项</x:v>
       </x:c>
-      <x:c r="C160" s="20" t="str">
+      <x:c r="C171" s="20" t="str">
         <x:v>待品牌正式服务确认</x:v>
       </x:c>
-      <x:c r="D160" s="20" t="str">
+      <x:c r="D171" s="20" t="str">
         <x:v>不能由10万自述或年活动承诺代填</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="95" customHeight="1">
-      <x:c r="A161" s="20" t="str">
+    <x:row r="172" ht="95" customHeight="1">
+      <x:c r="A172" s="20" t="str">
         <x:v>BoL Selected</x:v>
       </x:c>
-      <x:c r="B161" s="20" t="str">
-        <x:v>最终规格价、到场、复购及退改适用条款</x:v>
-      </x:c>
-      <x:c r="C161" s="20" t="str">
-        <x:v>待当场结算和服务记录</x:v>
-      </x:c>
-      <x:c r="D161" s="20" t="str">
-        <x:v>1688是商品展示价；已售29不作实到</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" ht="95" customHeight="1">
-      <x:c r="A162" s="20" t="str">
+      <x:c r="B172" s="20" t="str">
+        <x:v>到场、复购及退改适用条款</x:v>
+      </x:c>
+      <x:c r="C172" s="20" t="str">
+        <x:v>后续以服务记录核实</x:v>
+      </x:c>
+      <x:c r="D172" s="20" t="str">
+        <x:v>会员价按用户决定停止追查，保留未公开；1688是展示价；已售29不作实到</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="95" customHeight="1">
+      <x:c r="A173" s="20" t="str">
         <x:v>钻石婚恋</x:v>
       </x:c>
-      <x:c r="B162" s="20" t="str">
+      <x:c r="B173" s="20" t="str">
         <x:v>服务期限、次数、合同退改、单次派对价</x:v>
       </x:c>
-      <x:c r="C162" s="20" t="str">
+      <x:c r="C173" s="20" t="str">
         <x:v>待合同或正式报价</x:v>
       </x:c>
-      <x:c r="D162" s="20" t="str">
+      <x:c r="D173" s="20" t="str">
         <x:v>30／60／100万起为项目费</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="95" customHeight="1">
-      <x:c r="A163" s="20" t="str">
+    <x:row r="174" ht="95" customHeight="1">
+      <x:c r="A174" s="20" t="str">
         <x:v>婚恋旅行</x:v>
       </x:c>
-      <x:c r="B163" s="20" t="str">
+      <x:c r="B174" s="20" t="str">
         <x:v>同一产品的收费、承办关系、实际成团</x:v>
       </x:c>
-      <x:c r="C163" s="20" t="str">
+      <x:c r="C174" s="20" t="str">
         <x:v>待品牌完整产品及交付证据</x:v>
       </x:c>
-      <x:c r="D163" s="20" t="str">
+      <x:c r="D174" s="20" t="str">
         <x:v>有旅行入口或户外海报不等于旅行经营已成立</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="95" customHeight="1">
-      <x:c r="A164" s="20" t="str">
+    <x:row r="175" ht="95" customHeight="1">
+      <x:c r="A175" s="20" t="str">
         <x:v>客户画像</x:v>
       </x:c>
-      <x:c r="B164" s="20" t="str">
+      <x:c r="B175" s="20" t="str">
         <x:v>付费客户的年龄收入、性格兴趣分布</x:v>
       </x:c>
-      <x:c r="C164" s="20" t="str">
+      <x:c r="C175" s="20" t="str">
         <x:v>待客户访谈与机构脱敏统计</x:v>
       </x:c>
-      <x:c r="D164" s="20" t="str">
+      <x:c r="D175" s="20" t="str">
         <x:v>当前分品牌定位、单场准入和公开样例</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="95" customHeight="1">
-      <x:c r="A165" s="20" t="str">
+    <x:row r="176" ht="95" customHeight="1">
+      <x:c r="A176" s="20" t="str">
         <x:v>市场份额</x:v>
       </x:c>
-      <x:c r="B165" s="20" t="str">
+      <x:c r="B176" s="20" t="str">
         <x:v>同口径行业总收入及前五同期收入</x:v>
       </x:c>
-      <x:c r="C165" s="20" t="str">
+      <x:c r="C176" s="20" t="str">
         <x:v>待原始统计或可核财务</x:v>
       </x:c>
-      <x:c r="D165" s="20" t="str">
+      <x:c r="D176" s="20" t="str">
         <x:v>保留空白，不以平台声量补份额</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="95" customHeight="1">
-      <x:c r="A166" s="20" t="str">
+    <x:row r="177" ht="95" customHeight="1">
+      <x:c r="A177" s="20" t="str">
         <x:v>自身验证</x:v>
       </x:c>
-      <x:c r="B166" s="20" t="str">
+      <x:c r="B177" s="20" t="str">
         <x:v>目标客户付费反馈与供应商同条件报价</x:v>
       </x:c>
-      <x:c r="C166" s="20" t="str">
+      <x:c r="C177" s="20" t="str">
         <x:v>Olivia及格格后续核实</x:v>
       </x:c>
-      <x:c r="D166" s="20" t="str">
+      <x:c r="D177" s="20" t="str">
         <x:v>当前暂无已确认资源和访谈结论</x:v>
       </x:c>
     </x:row>
@@ -7434,10 +7867,21 @@
     <x:hyperlink xmlns:ns146="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" ns146:id="rIdStudy146"/>
     <x:hyperlink xmlns:ns147="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" ns147:id="rIdStudy147"/>
     <x:hyperlink xmlns:ns148="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" ns148:id="rIdStudy148"/>
+    <x:hyperlink xmlns:ns149="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" ns149:id="rIdStudy149"/>
+    <x:hyperlink xmlns:ns150="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" ns150:id="rIdStudy150"/>
+    <x:hyperlink xmlns:ns151="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" ns151:id="rIdStudy151"/>
+    <x:hyperlink xmlns:ns152="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" ns152:id="rIdStudy152"/>
+    <x:hyperlink xmlns:ns153="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" ns153:id="rIdStudy153"/>
+    <x:hyperlink xmlns:ns154="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" ns154:id="rIdStudy154"/>
+    <x:hyperlink xmlns:ns155="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" ns155:id="rIdStudy155"/>
+    <x:hyperlink xmlns:ns156="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" ns156:id="rIdStudy156"/>
+    <x:hyperlink xmlns:ns157="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" ns157:id="rIdStudy157"/>
+    <x:hyperlink xmlns:ns158="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" ns158:id="rIdStudy158"/>
+    <x:hyperlink xmlns:ns159="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" ns159:id="rIdStudy159"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d0ef08eb06c419c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6d14847e5ea4dca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29701,7 +30145,7 @@
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb679e57d06ca4de8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcb77b01bf934374"/>
   </x:tableParts>
 </x:worksheet>
 </file>